--- a/data/Pets.xlsx
+++ b/data/Pets.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:V37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,19 +425,19 @@
         <v>图标</v>
       </c>
       <c r="I1" t="str">
+        <v>技能标识</v>
+      </c>
+      <c r="J1" t="str">
         <v>价格</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>暴击率</v>
       </c>
-      <c r="K1" t="str">
-        <v>技能标识</v>
-      </c>
       <c r="L1" t="str">
+        <v>暴击伤害</v>
+      </c>
+      <c r="M1" t="str">
         <v>治疗量</v>
-      </c>
-      <c r="M1" t="str">
-        <v>暴击伤害</v>
       </c>
       <c r="N1" t="str">
         <v>防御力</v>
@@ -446,21 +446,24 @@
         <v>生命值</v>
       </c>
       <c r="P1" t="str">
+        <v>闪避值</v>
+      </c>
+      <c r="Q1" t="str">
         <v>眩晕概率</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>眩晕时长(ms)</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>治疗触发概率</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>隐身概率</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>隐身时长(ms)</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>伤害倍率</v>
       </c>
     </row>
@@ -472,7 +475,7 @@
         <v>pet_slime</v>
       </c>
       <c r="C2" t="str">
-        <v>小史莱姆</v>
+        <v>铜雀</v>
       </c>
       <c r="D2" t="str">
         <v>N</v>
@@ -484,12 +487,12 @@
         <v>2</v>
       </c>
       <c r="G2" t="str">
-        <v>可爱的史莱姆，会自动攻击怪物</v>
+        <v>青铜器上的雀形小灵，为你自动拾取战场上的灵质碎片和灵币</v>
       </c>
       <c r="H2" t="str">
-        <v>🟢</v>
-      </c>
-      <c r="I2">
+        <v>🐦</v>
+      </c>
+      <c r="J2">
         <v>500</v>
       </c>
     </row>
@@ -501,7 +504,7 @@
         <v>pet_bat</v>
       </c>
       <c r="C3" t="str">
-        <v>小蝙蝠</v>
+        <v>墨蝠</v>
       </c>
       <c r="D3" t="str">
         <v>N</v>
@@ -513,12 +516,12 @@
         <v>1.8</v>
       </c>
       <c r="G3" t="str">
-        <v>夜晚的小蝙蝠，速度很快</v>
+        <v>书画墨迹凝成的小灵蝠，拾取动作极快</v>
       </c>
       <c r="H3" t="str">
         <v>🦇</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>400</v>
       </c>
     </row>
@@ -530,7 +533,7 @@
         <v>pet_chick</v>
       </c>
       <c r="C4" t="str">
-        <v>小鸡</v>
+        <v>金乌雏</v>
       </c>
       <c r="D4" t="str">
         <v>N</v>
@@ -542,15 +545,15 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="str">
-        <v>可爱的小鸡，偶尔会暴击</v>
+        <v>金乌的雏形——它偶尔在你眼前闪过一道灵光，那就是一次暴击</v>
       </c>
       <c r="H4" t="str">
-        <v>🐣</v>
-      </c>
-      <c r="I4">
+        <v>☀️</v>
+      </c>
+      <c r="J4">
         <v>450</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>2</v>
       </c>
     </row>
@@ -562,7 +565,7 @@
         <v>pet_rabbit</v>
       </c>
       <c r="C5" t="str">
-        <v>小兔子</v>
+        <v>月兔</v>
       </c>
       <c r="D5" t="str">
         <v>N</v>
@@ -574,12 +577,12 @@
         <v>2.2</v>
       </c>
       <c r="G5" t="str">
-        <v>蹦蹦跳跳的小兔子</v>
+        <v>玉兔跃过你的灵场，每跳一步多带一份灵币</v>
       </c>
       <c r="H5" t="str">
         <v>🐰</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>480</v>
       </c>
     </row>
@@ -591,7 +594,7 @@
         <v>pet_fire_spirit</v>
       </c>
       <c r="C6" t="str">
-        <v>火焰精灵</v>
+        <v>火羽朱雀</v>
       </c>
       <c r="D6" t="str">
         <v>R</v>
@@ -603,16 +606,16 @@
         <v>1.5</v>
       </c>
       <c r="G6" t="str">
-        <v>火焰精灵，攻击附带燃烧效果</v>
+        <v>朱雀在你的灵场中盘旋，邪灵被灼热灵光持续烫伤</v>
       </c>
       <c r="H6" t="str">
         <v>🔥</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="str">
+        <v>burn</v>
+      </c>
+      <c r="J6">
         <v>1000</v>
-      </c>
-      <c r="K6" t="str">
-        <v>burn</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +626,7 @@
         <v>pet_ice_fairy</v>
       </c>
       <c r="C7" t="str">
-        <v>冰霜仙子</v>
+        <v>冰魄凤凰</v>
       </c>
       <c r="D7" t="str">
         <v>R</v>
@@ -635,19 +638,19 @@
         <v>1.8</v>
       </c>
       <c r="G7" t="str">
-        <v>冰霜仙子，攻击有几率冻结敌人</v>
+        <v>冰凤掠过时冻结邪灵的能量流动</v>
       </c>
       <c r="H7" t="str">
         <v>❄️</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="str">
+        <v>freeze</v>
+      </c>
+      <c r="J7">
         <v>1000</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>5</v>
-      </c>
-      <c r="K7" t="str">
-        <v>freeze</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +661,7 @@
         <v>pet_wind_sprite</v>
       </c>
       <c r="C8" t="str">
-        <v>风精灵</v>
+        <v>木灵青龙</v>
       </c>
       <c r="D8" t="str">
         <v>R</v>
@@ -670,19 +673,19 @@
         <v>1.2</v>
       </c>
       <c r="G8" t="str">
-        <v>风精灵，速度极快</v>
+        <v>青龙的吐息在你身上停留，灵场持续修复</v>
       </c>
       <c r="H8" t="str">
-        <v>💨</v>
-      </c>
-      <c r="I8">
+        <v>🐉</v>
+      </c>
+      <c r="I8" t="str">
+        <v>swift</v>
+      </c>
+      <c r="J8">
         <v>900</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>8</v>
-      </c>
-      <c r="K8" t="str">
-        <v>swift</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +696,7 @@
         <v>pet_thunder_imp</v>
       </c>
       <c r="C9" t="str">
-        <v>雷电小鬼</v>
+        <v>金甲麒麟</v>
       </c>
       <c r="D9" t="str">
         <v>R</v>
@@ -705,16 +708,16 @@
         <v>1.6</v>
       </c>
       <c r="G9" t="str">
-        <v>雷电小鬼，攻击附带电击</v>
+        <v>麒麟踏过灵场，重击触发时额外爆发一次灵光</v>
       </c>
       <c r="H9" t="str">
-        <v>⚡</v>
-      </c>
-      <c r="I9">
+        <v>⚜️</v>
+      </c>
+      <c r="I9" t="str">
+        <v>shock</v>
+      </c>
+      <c r="J9">
         <v>1100</v>
-      </c>
-      <c r="K9" t="str">
-        <v>shock</v>
       </c>
     </row>
     <row r="10">
@@ -725,7 +728,7 @@
         <v>pet_flower_fairy</v>
       </c>
       <c r="C10" t="str">
-        <v>花仙子</v>
+        <v>莲花童子</v>
       </c>
       <c r="D10" t="str">
         <v>R</v>
@@ -737,18 +740,18 @@
         <v>2</v>
       </c>
       <c r="G10" t="str">
-        <v>花仙子，攻击时微量恢复生命</v>
+        <v>曼陀罗灵域中绽放的莲花之灵——每开一瓣都是生命力的回响</v>
       </c>
       <c r="H10" t="str">
-        <v>🌸</v>
-      </c>
-      <c r="I10">
+        <v>🪷</v>
+      </c>
+      <c r="I10" t="str">
+        <v>heal</v>
+      </c>
+      <c r="J10">
         <v>950</v>
       </c>
-      <c r="K10" t="str">
-        <v>heal</v>
-      </c>
-      <c r="L10">
+      <c r="M10">
         <v>5</v>
       </c>
     </row>
@@ -760,7 +763,7 @@
         <v>pet_shadow_cat</v>
       </c>
       <c r="C11" t="str">
-        <v>暗影猫</v>
+        <v>巴斯特之影</v>
       </c>
       <c r="D11" t="str">
         <v>R</v>
@@ -772,19 +775,19 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="str">
-        <v>暗影猫，暴击率较高</v>
+        <v>尼罗河冥界的猫灵，潜伏在沙金暗处，偶尔突然出击</v>
       </c>
       <c r="H11" t="str">
-        <v>🐈‍⬛</v>
-      </c>
-      <c r="I11">
+        <v>🐱</v>
+      </c>
+      <c r="I11" t="str">
+        <v>shadow</v>
+      </c>
+      <c r="J11">
         <v>1050</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>10</v>
-      </c>
-      <c r="K11" t="str">
-        <v>shadow</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +798,7 @@
         <v>pet_star_dragon</v>
       </c>
       <c r="C12" t="str">
-        <v>星龙</v>
+        <v>应龙</v>
       </c>
       <c r="D12" t="str">
         <v>SR</v>
@@ -807,21 +810,21 @@
         <v>1.2</v>
       </c>
       <c r="G12" t="str">
-        <v>传说中的星龙，拥有强大的力量</v>
+        <v>应龙的龙威震慑邪灵，紊乱能量在你面前更难凝聚</v>
       </c>
       <c r="H12" t="str">
         <v>🐉</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="str">
+        <v>star_breath</v>
+      </c>
+      <c r="J12">
         <v>2000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>10</v>
       </c>
-      <c r="K12" t="str">
-        <v>star_breath</v>
-      </c>
-      <c r="M12">
+      <c r="L12">
         <v>0.2</v>
       </c>
     </row>
@@ -833,7 +836,7 @@
         <v>pet_crystal_golem</v>
       </c>
       <c r="C13" t="str">
-        <v>水晶巨人</v>
+        <v>方尖碑灵</v>
       </c>
       <c r="D13" t="str">
         <v>SR</v>
@@ -845,16 +848,16 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="str">
-        <v>水晶巨人，攻击力高但速度慢</v>
+        <v>尼罗河灵域中方尖碑的精魂——走得慢，但每一击都沉重</v>
       </c>
       <c r="H13" t="str">
-        <v>💎</v>
-      </c>
-      <c r="I13">
+        <v>🗿</v>
+      </c>
+      <c r="I13" t="str">
+        <v>crush</v>
+      </c>
+      <c r="J13">
         <v>2200</v>
-      </c>
-      <c r="K13" t="str">
-        <v>crush</v>
       </c>
     </row>
     <row r="14">
@@ -865,7 +868,7 @@
         <v>pet_moon_wolf</v>
       </c>
       <c r="C14" t="str">
-        <v>月光狼</v>
+        <v>芬里尔之息</v>
       </c>
       <c r="D14" t="str">
         <v>SR</v>
@@ -877,21 +880,21 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>月光下的狼王，暴击能力强大</v>
+        <v>极寒灵域中巨狼的残影，在月下暴戾而精准</v>
       </c>
       <c r="H14" t="str">
         <v>🐺</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="str">
+        <v>moon_howl</v>
+      </c>
+      <c r="J14">
         <v>2100</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>15</v>
       </c>
-      <c r="K14" t="str">
-        <v>moon_howl</v>
-      </c>
-      <c r="M14">
+      <c r="L14">
         <v>0.25</v>
       </c>
     </row>
@@ -903,7 +906,7 @@
         <v>pet_ocean_spirit</v>
       </c>
       <c r="C15" t="str">
-        <v>海洋精灵</v>
+        <v>恒河莲鲤</v>
       </c>
       <c r="D15" t="str">
         <v>SR</v>
@@ -915,18 +918,18 @@
         <v>1.3</v>
       </c>
       <c r="G15" t="str">
-        <v>海洋精灵，攻击时恢复生命</v>
+        <v>曼陀罗灵域河中的灵鲤，游过时修复被紊乱撕裂的部分</v>
       </c>
       <c r="H15" t="str">
-        <v>🌊</v>
-      </c>
-      <c r="I15">
+        <v>🐟</v>
+      </c>
+      <c r="I15" t="str">
+        <v>tidal</v>
+      </c>
+      <c r="J15">
         <v>2000</v>
       </c>
-      <c r="K15" t="str">
-        <v>tidal</v>
-      </c>
-      <c r="L15">
+      <c r="M15">
         <v>10</v>
       </c>
     </row>
@@ -938,7 +941,7 @@
         <v>pet_forest_guardian</v>
       </c>
       <c r="C16" t="str">
-        <v>森林守护者</v>
+        <v>世界树之芽</v>
       </c>
       <c r="D16" t="str">
         <v>SR</v>
@@ -950,16 +953,16 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="str">
-        <v>森林守护者，攻防兼备</v>
+        <v>世界树在灵域中的投影——看不见全树，只有一个芽在你身边</v>
       </c>
       <c r="H16" t="str">
-        <v>🌲</v>
-      </c>
-      <c r="I16">
+        <v>🌱</v>
+      </c>
+      <c r="I16" t="str">
+        <v>nature</v>
+      </c>
+      <c r="J16">
         <v>2300</v>
-      </c>
-      <c r="K16" t="str">
-        <v>nature</v>
       </c>
       <c r="N16">
         <v>10</v>
@@ -973,7 +976,7 @@
         <v>pet_flame_tiger</v>
       </c>
       <c r="C17" t="str">
-        <v>烈焰虎</v>
+        <v>斯芬克斯灵</v>
       </c>
       <c r="D17" t="str">
         <v>SR</v>
@@ -985,19 +988,19 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="str">
-        <v>烈焰之虎，燃烧一切</v>
+        <v>尼罗河冥界的狮身之灵，燃烧的沙金是它的皮肤</v>
       </c>
       <c r="H17" t="str">
-        <v>🐯</v>
-      </c>
-      <c r="I17">
+        <v>🦁</v>
+      </c>
+      <c r="I17" t="str">
+        <v>flame</v>
+      </c>
+      <c r="J17">
         <v>2400</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>12</v>
-      </c>
-      <c r="K17" t="str">
-        <v>flame</v>
       </c>
     </row>
     <row r="18">
@@ -1008,7 +1011,7 @@
         <v>pet_frost_fox</v>
       </c>
       <c r="C18" t="str">
-        <v>冰霜狐</v>
+        <v>冰霜巨狼</v>
       </c>
       <c r="D18" t="str">
         <v>SR</v>
@@ -1020,21 +1023,21 @@
         <v>0.9</v>
       </c>
       <c r="G18" t="str">
-        <v>冰霜狐，极高的暴击能力</v>
+        <v>极寒灵域中的白狼，极夜中唯一的狩猎者</v>
       </c>
       <c r="H18" t="str">
-        <v>🦊</v>
-      </c>
-      <c r="I18">
+        <v>🐺</v>
+      </c>
+      <c r="I18" t="str">
+        <v>frost</v>
+      </c>
+      <c r="J18">
         <v>2200</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>18</v>
       </c>
-      <c r="K18" t="str">
-        <v>frost</v>
-      </c>
-      <c r="M18">
+      <c r="L18">
         <v>0.3</v>
       </c>
     </row>
@@ -1058,21 +1061,21 @@
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>浴火重生的凤凰</v>
+        <v>浴火重生的华夏神禽——每次从紊乱中复出都更强</v>
       </c>
       <c r="H19" t="str">
         <v>🦅</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="str">
+        <v>rebirth</v>
+      </c>
+      <c r="J19">
         <v>5000</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>15</v>
       </c>
-      <c r="K19" t="str">
-        <v>rebirth</v>
-      </c>
-      <c r="M19">
+      <c r="L19">
         <v>0.3</v>
       </c>
     </row>
@@ -1084,7 +1087,7 @@
         <v>pet_dragon_turtle</v>
       </c>
       <c r="C20" t="str">
-        <v>龙龟</v>
+        <v>赑屃</v>
       </c>
       <c r="D20" t="str">
         <v>SSR</v>
@@ -1096,16 +1099,16 @@
         <v>1.8</v>
       </c>
       <c r="G20" t="str">
-        <v>龙龟，极其坚固</v>
+        <v>龙生九子中的负重者——天生比任何灵兽都厚重</v>
       </c>
       <c r="H20" t="str">
         <v>🐢</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="str">
+        <v>shell</v>
+      </c>
+      <c r="J20">
         <v>4800</v>
-      </c>
-      <c r="K20" t="str">
-        <v>shell</v>
       </c>
       <c r="N20">
         <v>30</v>
@@ -1122,7 +1125,7 @@
         <v>pet_unicorn</v>
       </c>
       <c r="C21" t="str">
-        <v>独角兽</v>
+        <v>麒麟</v>
       </c>
       <c r="D21" t="str">
         <v>SSR</v>
@@ -1134,25 +1137,25 @@
         <v>0.8</v>
       </c>
       <c r="G21" t="str">
-        <v>神圣独角兽，暴击和治疗兼备</v>
+        <v>麒麟踏灵而来，暴击中带来治愈之力</v>
       </c>
       <c r="H21" t="str">
         <v>🦄</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="str">
+        <v>holy</v>
+      </c>
+      <c r="J21">
         <v>5200</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>25</v>
       </c>
-      <c r="K21" t="str">
-        <v>holy</v>
-      </c>
       <c r="L21">
+        <v>0.4</v>
+      </c>
+      <c r="M21">
         <v>15</v>
-      </c>
-      <c r="M21">
-        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -1163,7 +1166,7 @@
         <v>pet_void_serpent</v>
       </c>
       <c r="C22" t="str">
-        <v>虚空蛇</v>
+        <v>尘世巨蟒</v>
       </c>
       <c r="D22" t="str">
         <v>SSR</v>
@@ -1175,21 +1178,21 @@
         <v>1.1</v>
       </c>
       <c r="G22" t="str">
-        <v>虚空蛇，撕裂空间的力量</v>
+        <v>耶梦加得的残影在极寒灵域中沉睡——撕裂空间的，是它的呼吸</v>
       </c>
       <c r="H22" t="str">
         <v>🐍</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="str">
+        <v>void</v>
+      </c>
+      <c r="J22">
         <v>5100</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>20</v>
       </c>
-      <c r="K22" t="str">
-        <v>void</v>
-      </c>
-      <c r="M22">
+      <c r="L22">
         <v>0.35</v>
       </c>
     </row>
@@ -1201,7 +1204,7 @@
         <v>pet_celestial_deer</v>
       </c>
       <c r="C23" t="str">
-        <v>天鹿</v>
+        <v>白泽之角</v>
       </c>
       <c r="D23" t="str">
         <v>SSR</v>
@@ -1213,21 +1216,21 @@
         <v>0.9</v>
       </c>
       <c r="G23" t="str">
-        <v>天鹿，神圣的治愈之力</v>
+        <v>白泽的一只角化作灵物——让你直接看到邪灵的破绽</v>
       </c>
       <c r="H23" t="str">
         <v>🦌</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="str">
+        <v>celestial</v>
+      </c>
+      <c r="J23">
         <v>5000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>30</v>
       </c>
-      <c r="K23" t="str">
-        <v>celestial</v>
-      </c>
-      <c r="L23">
+      <c r="M23">
         <v>20</v>
       </c>
     </row>
@@ -1239,7 +1242,7 @@
         <v>pet_thunder_dragon</v>
       </c>
       <c r="C24" t="str">
-        <v>雷龙</v>
+        <v>夔龙</v>
       </c>
       <c r="D24" t="str">
         <v>SSR</v>
@@ -1251,21 +1254,21 @@
         <v>1.2</v>
       </c>
       <c r="G24" t="str">
-        <v>雷龙，雷霆万钧</v>
+        <v>雷泽中的雷兽——一足而立，一吼金雷万钧</v>
       </c>
       <c r="H24" t="str">
-        <v>🐲</v>
-      </c>
-      <c r="I24">
+        <v>🐉</v>
+      </c>
+      <c r="I24" t="str">
+        <v>thunder</v>
+      </c>
+      <c r="J24">
         <v>5500</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>18</v>
       </c>
-      <c r="K24" t="str">
-        <v>thunder</v>
-      </c>
-      <c r="M24">
+      <c r="L24">
         <v>0.35</v>
       </c>
     </row>
@@ -1277,7 +1280,7 @@
         <v>pet_galaxy_dragon</v>
       </c>
       <c r="C25" t="str">
-        <v>星河龙</v>
+        <v>烛龙</v>
       </c>
       <c r="D25" t="str">
         <v>UR</v>
@@ -1289,21 +1292,21 @@
         <v>0.8</v>
       </c>
       <c r="G25" t="str">
-        <v>星河龙，跨越宇宙的神兽</v>
+        <v>烛龙盘踞在你的灵场——它睁眼，灵域多了光亮；闭眼，邪灵多了迷惘</v>
       </c>
       <c r="H25" t="str">
-        <v>🌌</v>
-      </c>
-      <c r="I25">
+        <v>🐉</v>
+      </c>
+      <c r="I25" t="str">
+        <v>galaxy_breath</v>
+      </c>
+      <c r="J25">
         <v>15000</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>30</v>
       </c>
-      <c r="K25" t="str">
-        <v>galaxy_breath</v>
-      </c>
-      <c r="M25">
+      <c r="L25">
         <v>0.5</v>
       </c>
     </row>
@@ -1315,7 +1318,7 @@
         <v>pet_primordial_phoenix</v>
       </c>
       <c r="C26" t="str">
-        <v>始祖凤凰</v>
+        <v>祖凤</v>
       </c>
       <c r="D26" t="str">
         <v>UR</v>
@@ -1327,25 +1330,25 @@
         <v>0.7</v>
       </c>
       <c r="G26" t="str">
-        <v>始祖凤凰，不死不灭</v>
+        <v>凤的祖灵——不死不灭的洪荒之灵</v>
       </c>
       <c r="H26" t="str">
         <v>🔥</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="str">
+        <v>eternal_flame</v>
+      </c>
+      <c r="J26">
         <v>12000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>35</v>
       </c>
-      <c r="K26" t="str">
-        <v>eternal_flame</v>
-      </c>
       <c r="L26">
+        <v>0.6</v>
+      </c>
+      <c r="M26">
         <v>30</v>
-      </c>
-      <c r="M26">
-        <v>0.6</v>
       </c>
     </row>
     <row r="27">
@@ -1356,7 +1359,7 @@
         <v>pet_chaos_beast</v>
       </c>
       <c r="C27" t="str">
-        <v>混沌兽</v>
+        <v>贝努鸟灵</v>
       </c>
       <c r="D27" t="str">
         <v>UR</v>
@@ -1368,21 +1371,21 @@
         <v>1</v>
       </c>
       <c r="G27" t="str">
-        <v>混沌初开时的神兽</v>
+        <v>尼罗河冥界中与太阳同升的神鸟——每一次日出都是重生</v>
       </c>
       <c r="H27" t="str">
-        <v>👹</v>
-      </c>
-      <c r="I27">
+        <v>🦅</v>
+      </c>
+      <c r="I27" t="str">
+        <v>chaos</v>
+      </c>
+      <c r="J27">
         <v>18000</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>25</v>
       </c>
-      <c r="K27" t="str">
-        <v>chaos</v>
-      </c>
-      <c r="M27">
+      <c r="L27">
         <v>0.7</v>
       </c>
     </row>
@@ -1394,7 +1397,7 @@
         <v>pet_star_goddess_pet</v>
       </c>
       <c r="C28" t="str">
-        <v>星神使者</v>
+        <v>努特之翼</v>
       </c>
       <c r="D28" t="str">
         <v>UR</v>
@@ -1406,25 +1409,25 @@
         <v>0.6</v>
       </c>
       <c r="G28" t="str">
-        <v>星之女神的信使，全能神宠</v>
+        <v>埃及天空女神努特展开的羽翼——从天空俯视时，看到了灵域的全部</v>
       </c>
       <c r="H28" t="str">
         <v>🌟</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="str">
+        <v>divine</v>
+      </c>
+      <c r="J28">
         <v>20000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>40</v>
       </c>
-      <c r="K28" t="str">
-        <v>divine</v>
-      </c>
       <c r="L28">
+        <v>0.5</v>
+      </c>
+      <c r="M28">
         <v>25</v>
-      </c>
-      <c r="M28">
-        <v>0.5</v>
       </c>
       <c r="N28">
         <v>20</v>
@@ -1438,7 +1441,7 @@
         <v>pet_void_sprite</v>
       </c>
       <c r="C29" t="str">
-        <v>虚空小精灵</v>
+        <v>灵脉小灵</v>
       </c>
       <c r="D29" t="str">
         <v>SSR</v>
@@ -1450,18 +1453,18 @@
         <v>1.2</v>
       </c>
       <c r="G29" t="str">
-        <v>攻击时10%概率使怪物眩晕1秒</v>
+        <v>灵脉交叉处偶然产生的小型灵能聚合体——喜欢帮你找到邪灵的破绽</v>
       </c>
       <c r="H29" t="str">
-        <v>🌀</v>
-      </c>
-      <c r="K29" t="str">
+        <v>✨</v>
+      </c>
+      <c r="I29" t="str">
         <v>void_stun</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>0.1</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>1</v>
       </c>
     </row>
@@ -1473,7 +1476,7 @@
         <v>pet_star_devourer_cub</v>
       </c>
       <c r="C30" t="str">
-        <v>星渊幼崽</v>
+        <v>灵脉涡兽</v>
       </c>
       <c r="D30" t="str">
         <v>SSR</v>
@@ -1485,18 +1488,18 @@
         <v>1.5</v>
       </c>
       <c r="G30" t="str">
-        <v>攻击时15%概率为玩家回复5HP</v>
+        <v>灵脉中小型紊乱涡流的聚合体——吃掉紊乱，吐出治愈</v>
       </c>
       <c r="H30" t="str">
-        <v>🐉</v>
-      </c>
-      <c r="K30" t="str">
+        <v>🌀</v>
+      </c>
+      <c r="I30" t="str">
         <v>devourer_heal</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>5</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>0.15</v>
       </c>
     </row>
@@ -1508,7 +1511,7 @@
         <v>pet_phantom_hunter</v>
       </c>
       <c r="C31" t="str">
-        <v>幻影猎手</v>
+        <v>玛雅豹灵</v>
       </c>
       <c r="D31" t="str">
         <v>UR</v>
@@ -1520,21 +1523,21 @@
         <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v>攻击时20%概率隐身1秒，期间双倍攻击</v>
+        <v>丛林灵域中的夜行猎手——隐身的两秒内，它攒着所有没能释放的爆发</v>
       </c>
       <c r="H31" t="str">
-        <v>👻</v>
-      </c>
-      <c r="K31" t="str">
+        <v>🐆</v>
+      </c>
+      <c r="I31" t="str">
         <v>phantom_strike</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>0.2</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>1</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>2</v>
       </c>
     </row>
@@ -1546,7 +1549,7 @@
         <v>pet_star_mite</v>
       </c>
       <c r="C32" t="str">
-        <v>星尘虫</v>
+        <v>灵尘虫</v>
       </c>
       <c r="D32" t="str">
         <v>UC</v>
@@ -1558,12 +1561,12 @@
         <v>2.8</v>
       </c>
       <c r="G32" t="str">
-        <v>微小星尘虫，攻速快但伤害低</v>
+        <v>最微小的灵能体，数量最多的伴随者——攻速极快</v>
       </c>
       <c r="H32" t="str">
         <v>🐛</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>200</v>
       </c>
     </row>
@@ -1575,7 +1578,7 @@
         <v>pet_dust_wisp</v>
       </c>
       <c r="C33" t="str">
-        <v>尘埃精灵</v>
+        <v>沙灵</v>
       </c>
       <c r="D33" t="str">
         <v>UC</v>
@@ -1587,15 +1590,15 @@
         <v>2.5</v>
       </c>
       <c r="G33" t="str">
-        <v>星尘凝聚的小精灵，偶尔暴击</v>
+        <v>尼罗河灵域中的沙金微尘凝聚成的小型伴随灵</v>
       </c>
       <c r="H33" t="str">
-        <v>💭</v>
-      </c>
-      <c r="I33">
+        <v>🏜️</v>
+      </c>
+      <c r="J33">
         <v>250</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>1</v>
       </c>
     </row>
@@ -1607,7 +1610,7 @@
         <v>pet_world_eater</v>
       </c>
       <c r="C34" t="str">
-        <v>噬界虫</v>
+        <v>亚历山大虫灵</v>
       </c>
       <c r="D34" t="str">
         <v>LR</v>
@@ -1619,18 +1622,18 @@
         <v>0.6</v>
       </c>
       <c r="G34" t="str">
-        <v>吞噬星球的巨虫，20%概率造成3倍伤害</v>
+        <v>亚历山大图书馆焚毁莎草纸卷散落的灵——不是它吃了世界，是它身上结晶了历史</v>
       </c>
       <c r="H34" t="str">
-        <v>🐛</v>
-      </c>
-      <c r="I34">
+        <v>📜</v>
+      </c>
+      <c r="J34">
         <v>50000</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>35</v>
       </c>
-      <c r="M34">
+      <c r="L34">
         <v>0.8</v>
       </c>
     </row>
@@ -1642,7 +1645,7 @@
         <v>pet_nebula_serpent</v>
       </c>
       <c r="C35" t="str">
-        <v>星云巨蛇</v>
+        <v>羽蛇神之影</v>
       </c>
       <c r="D35" t="str">
         <v>LR</v>
@@ -1654,18 +1657,18 @@
         <v>0.8</v>
       </c>
       <c r="G35" t="str">
-        <v>每次攻击使目标受伤+5%（最多叠10层）</v>
+        <v>羽蛇神在灵域中走过留下的残影——不是星空，是丛林上的夜天</v>
       </c>
       <c r="H35" t="str">
         <v>🐍</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>48000</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>30</v>
       </c>
-      <c r="M35">
+      <c r="L35">
         <v>0.7</v>
       </c>
     </row>
@@ -1677,7 +1680,7 @@
         <v>pet_festival_lantern</v>
       </c>
       <c r="C36" t="str">
-        <v>星灯精灵</v>
+        <v>灯灵</v>
       </c>
       <c r="D36" t="str">
         <v>SP</v>
@@ -1689,18 +1692,18 @@
         <v>1</v>
       </c>
       <c r="G36" t="str">
-        <v>场上星星分数+10%，每5次点击释放星火</v>
+        <v>蜀汉城灵节上无数灯笼的灵汇聚成的伴随灵</v>
       </c>
       <c r="H36" t="str">
         <v>🏮</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>30000</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>25</v>
       </c>
-      <c r="M36">
+      <c r="L36">
         <v>0.5</v>
       </c>
     </row>
@@ -1712,7 +1715,7 @@
         <v>pet_meteor_fox</v>
       </c>
       <c r="C37" t="str">
-        <v>流星狐</v>
+        <v>天狐</v>
       </c>
       <c r="D37" t="str">
         <v>SP</v>
@@ -1724,24 +1727,24 @@
         <v>0.9</v>
       </c>
       <c r="G37" t="str">
-        <v>暴击时留下流星，3秒后爆炸100范围伤害</v>
+        <v>浮世灵域中高高跳过的狐灵——经过的地方留下流星，流星过后是爆炸</v>
       </c>
       <c r="H37" t="str">
         <v>🦊</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>28000</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>35</v>
       </c>
-      <c r="M37">
+      <c r="L37">
         <v>0.45</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V37"/>
   </ignoredErrors>
 </worksheet>
 </file>